--- a/نموذج الأصناف.xlsx
+++ b/نموذج الأصناف.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ireac\Documents\GitHub\MZ.S-ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B2A6F0-2B83-4024-8334-586F1BB08057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8EF832-EB49-47BF-AE35-7953ADDA1207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="135">
   <si>
     <t>code</t>
   </si>
@@ -409,9 +409,6 @@
   </si>
   <si>
     <t>كروت علف دجاج بادي بياض (قديمة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قطع غيار / معدات صيانة </t>
   </si>
   <si>
     <t>كروت بياض مرحلة الإنتاج (معدل وراثي)</t>
@@ -886,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.59765625" customWidth="1"/>
@@ -2751,7 +2748,7 @@
     </row>
     <row r="86" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>22000.400000000001</v>
+        <v>22000.41</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>107</v>
@@ -2770,7 +2767,7 @@
     </row>
     <row r="87" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>22000.41</v>
+        <v>22000.42</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>108</v>
@@ -2789,7 +2786,7 @@
     </row>
     <row r="88" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>22000.42</v>
+        <v>22000.43</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>109</v>
@@ -2808,10 +2805,10 @@
     </row>
     <row r="89" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>22000.43</v>
+        <v>22000.44</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
@@ -2827,10 +2824,10 @@
     </row>
     <row r="90" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>22000.44</v>
+        <v>22000.45</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
@@ -2846,10 +2843,10 @@
     </row>
     <row r="91" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>22000.45</v>
+        <v>22000.46</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
@@ -2868,10 +2865,10 @@
         <v>133000.1</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>10</v>
@@ -2882,10 +2879,10 @@
         <v>133000.20000000001</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>10</v>
@@ -2893,29 +2890,15 @@
     </row>
     <row r="94" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>133000.29999999999</v>
+        <v>133000.4</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
-        <v>133000.4</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E95" s="2" t="s">
         <v>10</v>
       </c>
     </row>
